--- a/data/out/variants/v5_no_fuel_and_cost_lags/summary_v5_no_fuel_and_cost_lags.xlsx
+++ b/data/out/variants/v5_no_fuel_and_cost_lags/summary_v5_no_fuel_and_cost_lags.xlsx
@@ -526,7 +526,7 @@
         <v>0.9466712185560131</v>
       </c>
       <c r="F2" t="n">
-        <v>46.96978888088318</v>
+        <v>46.96978888088308</v>
       </c>
       <c r="G2" t="n">
         <v>13407.7832555425</v>
@@ -535,7 +535,7 @@
         <v>115.7919826911281</v>
       </c>
       <c r="I2" t="n">
-        <v>11.56683288053708</v>
+        <v>11.56683288053703</v>
       </c>
       <c r="J2" t="n">
         <v>48168</v>
@@ -547,7 +547,7 @@
         <v>9634</v>
       </c>
       <c r="M2" t="n">
-        <v>0.08215618133544922</v>
+        <v>0.07143592834472656</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -574,19 +574,19 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>0.9466687316563154</v>
+        <v>0.9466687177659967</v>
       </c>
       <c r="F3" t="n">
-        <v>46.98203966988714</v>
+        <v>46.98206488718608</v>
       </c>
       <c r="G3" t="n">
-        <v>13408.40850538365</v>
+        <v>13408.41199765137</v>
       </c>
       <c r="H3" t="n">
-        <v>115.7946825436455</v>
+        <v>115.7946976232132</v>
       </c>
       <c r="I3" t="n">
-        <v>11.5695153425511</v>
+        <v>11.56952513924947</v>
       </c>
       <c r="J3" t="n">
         <v>48168</v>
@@ -598,7 +598,7 @@
         <v>9634</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05321073532104492</v>
+        <v>0.05787253379821777</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -625,19 +625,19 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.9467876277073205</v>
+        <v>0.9467790580457282</v>
       </c>
       <c r="F4" t="n">
-        <v>46.44343306008406</v>
+        <v>46.49103193774706</v>
       </c>
       <c r="G4" t="n">
-        <v>13378.51597008371</v>
+        <v>13380.67053206867</v>
       </c>
       <c r="H4" t="n">
-        <v>115.6655349275821</v>
+        <v>115.6748483122786</v>
       </c>
       <c r="I4" t="n">
-        <v>11.33869725130783</v>
+        <v>11.36099225689346</v>
       </c>
       <c r="J4" t="n">
         <v>48168</v>
@@ -649,7 +649,7 @@
         <v>9634</v>
       </c>
       <c r="M4" t="n">
-        <v>1.811560153961182</v>
+        <v>2.989743232727051</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9465573143900419</v>
+        <v>0.9465556981923459</v>
       </c>
       <c r="F5" t="n">
-        <v>47.41945457959511</v>
+        <v>47.42284204291035</v>
       </c>
       <c r="G5" t="n">
-        <v>13436.4207441161</v>
+        <v>13436.82708432902</v>
       </c>
       <c r="H5" t="n">
-        <v>115.9155759340223</v>
+        <v>115.9173286628407</v>
       </c>
       <c r="I5" t="n">
-        <v>11.64577299999411</v>
+        <v>11.64724312607742</v>
       </c>
       <c r="J5" t="n">
         <v>48168</v>
@@ -704,7 +704,7 @@
         <v>9634</v>
       </c>
       <c r="M5" t="n">
-        <v>15.48801779747009</v>
+        <v>33.31830859184265</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-38.47495200504483</v>
+        <v>-38.47372806566734</v>
       </c>
     </row>
     <row r="6">
@@ -740,16 +740,16 @@
         <v>0.8414632613956305</v>
       </c>
       <c r="F6" t="n">
-        <v>74.49491854489354</v>
+        <v>74.49491854489358</v>
       </c>
       <c r="G6" t="n">
-        <v>39858.89367227723</v>
+        <v>39858.89367227724</v>
       </c>
       <c r="H6" t="n">
         <v>199.6469225214284</v>
       </c>
       <c r="I6" t="n">
-        <v>11.67003922183371</v>
+        <v>11.67003922183376</v>
       </c>
       <c r="J6" t="n">
         <v>48168</v>
@@ -761,7 +761,7 @@
         <v>9634</v>
       </c>
       <c r="M6" t="n">
-        <v>3.092097520828247</v>
+        <v>8.848148584365845</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-73.61256027553885</v>
+        <v>-72.41777297038222</v>
       </c>
     </row>
     <row r="7">
@@ -794,19 +794,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8152248778385406</v>
+        <v>0.8157692825065334</v>
       </c>
       <c r="F7" t="n">
-        <v>76.01297975468962</v>
+        <v>75.96629244734663</v>
       </c>
       <c r="G7" t="n">
-        <v>46455.67968882554</v>
+        <v>46318.80688592041</v>
       </c>
       <c r="H7" t="n">
-        <v>215.5357967689487</v>
+        <v>215.2180449821074</v>
       </c>
       <c r="I7" t="n">
-        <v>11.4403709453451</v>
+        <v>11.44167819068512</v>
       </c>
       <c r="J7" t="n">
         <v>48168</v>
@@ -818,7 +818,7 @@
         <v>9634</v>
       </c>
       <c r="M7" t="n">
-        <v>2869.274785995483</v>
+        <v>3516.303617715836</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-76.30026486269786</v>
+        <v>-76.30067003705609</v>
       </c>
     </row>
     <row r="8">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7464000733515593</v>
+        <v>0.7451391794917921</v>
       </c>
       <c r="F8" t="n">
-        <v>87.98844701272428</v>
+        <v>88.20167875259543</v>
       </c>
       <c r="G8" t="n">
-        <v>63759.43267511439</v>
+        <v>64076.44332344059</v>
       </c>
       <c r="H8" t="n">
-        <v>252.506302248309</v>
+        <v>253.1332521093201</v>
       </c>
       <c r="I8" t="n">
-        <v>12.66324716754144</v>
+        <v>12.67571535768397</v>
       </c>
       <c r="J8" t="n">
         <v>48168</v>
@@ -875,7 +875,7 @@
         <v>9634</v>
       </c>
       <c r="M8" t="n">
-        <v>1756.409390449524</v>
+        <v>1484.742160081863</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-64.27325776083525</v>
+        <v>-63.70843822892639</v>
       </c>
     </row>
     <row r="9">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.2241519135408038</v>
+        <v>0.2240481314125174</v>
       </c>
       <c r="F9" t="n">
-        <v>209.2434417421432</v>
+        <v>210.3671692213294</v>
       </c>
       <c r="G9" t="n">
-        <v>195061.7040330899</v>
+        <v>195087.7966653269</v>
       </c>
       <c r="H9" t="n">
-        <v>441.6579038499028</v>
+        <v>441.6874422771456</v>
       </c>
       <c r="I9" t="n">
-        <v>46.16849107291696</v>
+        <v>46.84981207897248</v>
       </c>
       <c r="J9" t="n">
         <v>48168</v>
@@ -932,7 +932,7 @@
         <v>9634</v>
       </c>
       <c r="M9" t="n">
-        <v>588.3193004131317</v>
+        <v>488.1216642856598</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>-201.6608737065262</v>
+        <v>-201.4588537502169</v>
       </c>
     </row>
     <row r="10">
@@ -965,19 +965,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7469000590568616</v>
+        <v>0.7458325340450151</v>
       </c>
       <c r="F10" t="n">
-        <v>134.2199556629793</v>
+        <v>135.5255501349388</v>
       </c>
       <c r="G10" t="n">
-        <v>63633.72757205285</v>
+        <v>63902.12192855511</v>
       </c>
       <c r="H10" t="n">
-        <v>252.2572646566454</v>
+        <v>252.7886902702633</v>
       </c>
       <c r="I10" t="n">
-        <v>35.10165246005241</v>
+        <v>35.22813936894995</v>
       </c>
       <c r="J10" t="n">
         <v>48168</v>
@@ -989,7 +989,7 @@
         <v>9634</v>
       </c>
       <c r="M10" t="n">
-        <v>7.462559461593628</v>
+        <v>6.594917774200439</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-106.8341789968688</v>
+        <v>-107.1061596710511</v>
       </c>
     </row>
     <row r="11">
@@ -1018,23 +1018,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 397, 'learning_rate': 0.022350212090831458, 'max_depth': 4, 'subsample': 0.9156325820701448, 'colsample_bytree': 0.8569664296384512}</t>
+          <t>{'n_estimators': 812, 'learning_rate': 0.01447897660851035, 'max_depth': 3, 'subsample': 0.6603256072788306, 'colsample_bytree': 0.6619928936149252}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8152506999432512</v>
+        <v>0.8175494562294807</v>
       </c>
       <c r="F11" t="n">
-        <v>77.2670218218296</v>
+        <v>78.19963992013707</v>
       </c>
       <c r="G11" t="n">
-        <v>46449.18756255174</v>
+        <v>45871.24024763975</v>
       </c>
       <c r="H11" t="n">
-        <v>215.5207358064456</v>
+        <v>214.1757228250666</v>
       </c>
       <c r="I11" t="n">
-        <v>11.79517881145096</v>
+        <v>12.24638084309412</v>
       </c>
       <c r="J11" t="n">
         <v>48168</v>
@@ -1046,7 +1046,7 @@
         <v>9634</v>
       </c>
       <c r="M11" t="n">
-        <v>207.606867313385</v>
+        <v>232.719598531723</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1073,23 +1073,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 648, 'learning_rate': 0.010015234836278973, 'num_leaves': 32, 'min_child_samples': 37}</t>
+          <t>{'n_estimators': 408, 'learning_rate': 0.012721751149416916, 'num_leaves': 110, 'min_child_samples': 36}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.8058411203258797</v>
+        <v>0.8109518416672921</v>
       </c>
       <c r="F12" t="n">
-        <v>77.96628029842104</v>
+        <v>78.19430516783099</v>
       </c>
       <c r="G12" t="n">
-        <v>48814.91954853383</v>
+        <v>47529.99530744451</v>
       </c>
       <c r="H12" t="n">
-        <v>220.9409865745463</v>
+        <v>218.0137502715012</v>
       </c>
       <c r="I12" t="n">
-        <v>11.04927342588808</v>
+        <v>11.38530192035236</v>
       </c>
       <c r="J12" t="n">
         <v>48168</v>
@@ -1101,7 +1101,7 @@
         <v>9634</v>
       </c>
       <c r="M12" t="n">
-        <v>688.5601961612701</v>
+        <v>420.0621790885925</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1128,23 +1128,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'iterations': 610, 'learning_rate': 0.015403877635688163, 'depth': 4}</t>
+          <t>{'iterations': 410, 'learning_rate': 0.027497471934662898, 'depth': 4}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.8114773999863142</v>
+        <v>0.8113413501735308</v>
       </c>
       <c r="F13" t="n">
-        <v>79.60843156655615</v>
+        <v>80.05767988340338</v>
       </c>
       <c r="G13" t="n">
-        <v>47397.86080448391</v>
+        <v>47432.06609386732</v>
       </c>
       <c r="H13" t="n">
-        <v>217.7104976901296</v>
+        <v>217.7890403437862</v>
       </c>
       <c r="I13" t="n">
-        <v>12.28914109243857</v>
+        <v>12.57488601362153</v>
       </c>
       <c r="J13" t="n">
         <v>48168</v>
@@ -1156,7 +1156,7 @@
         <v>9634</v>
       </c>
       <c r="M13" t="n">
-        <v>530.0725426673889</v>
+        <v>453.022670507431</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1183,23 +1183,23 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'max_depth': 10, 'min_samples_split': 5, 'n_estimators': 300}</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.7911067879519263</v>
+        <v>0.7870229568122911</v>
       </c>
       <c r="F14" t="n">
-        <v>80.18104543458085</v>
+        <v>83.7404784409383</v>
       </c>
       <c r="G14" t="n">
-        <v>52519.38699624006</v>
+        <v>53546.13317888021</v>
       </c>
       <c r="H14" t="n">
-        <v>229.1710867370491</v>
+        <v>231.4003741977964</v>
       </c>
       <c r="I14" t="n">
-        <v>11.78308409708962</v>
+        <v>13.1531540964381</v>
       </c>
       <c r="J14" t="n">
         <v>48168</v>
@@ -1211,7 +1211,7 @@
         <v>9634</v>
       </c>
       <c r="M14" t="n">
-        <v>287.8872816562653</v>
+        <v>473.3494369983673</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>-69.74622428669717</v>
+        <v>-70.29549493078252</v>
       </c>
     </row>
     <row r="15">
@@ -1268,7 +1268,7 @@
         <v>9634</v>
       </c>
       <c r="M15" t="n">
-        <v>26.97985100746155</v>
+        <v>43.7507655620575</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1297,23 +1297,23 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'alpha': 0.01, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.001}</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.001}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.939640228209209</v>
+        <v>0.9447025393039328</v>
       </c>
       <c r="F16" t="n">
-        <v>52.65533674922548</v>
+        <v>50.99333046203331</v>
       </c>
       <c r="G16" t="n">
-        <v>15175.49652573556</v>
+        <v>13902.74346271133</v>
       </c>
       <c r="H16" t="n">
-        <v>123.1888652668558</v>
+        <v>117.9098955249784</v>
       </c>
       <c r="I16" t="n">
-        <v>12.26130600819354</v>
+        <v>13.03068391220395</v>
       </c>
       <c r="J16" t="n">
         <v>48168</v>
@@ -1325,7 +1325,7 @@
         <v>9634</v>
       </c>
       <c r="M16" t="n">
-        <v>729.2812123298645</v>
+        <v>1565.54877114296</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>-40.79064795887722</v>
+        <v>-40.0066051317231</v>
       </c>
     </row>
   </sheetData>
